--- a/forms/trg/Formulir_TRG_wte.xlsx
+++ b/forms/trg/Formulir_TRG_wte.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Eng. Ir. Andi Erwin Eka Putra, ST. MT.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
@@ -943,7 +947,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -976,7 +980,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1009,7 +1013,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1042,7 +1046,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1075,7 +1079,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1108,7 +1112,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1174,7 +1178,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1207,7 +1211,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1240,7 +1244,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1273,7 +1277,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1306,7 +1310,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1339,7 +1343,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1372,7 +1376,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -1405,7 +1409,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="12" t="n"/>
@@ -1438,7 +1442,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
@@ -1471,7 +1475,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="12" t="n"/>
@@ -1504,7 +1508,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="12" t="n"/>
@@ -1537,7 +1541,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="12" t="n"/>
@@ -1570,7 +1574,7 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
@@ -1603,7 +1607,7 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D26" s="12" t="n"/>
@@ -1636,7 +1640,7 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D27" s="12" t="n"/>
@@ -1669,7 +1673,7 @@
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D28" s="12" t="n"/>
@@ -1702,7 +1706,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D29" s="12" t="n"/>
@@ -1735,7 +1739,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D30" s="12" t="n"/>
@@ -1768,7 +1772,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D31" s="12" t="n"/>
@@ -1801,7 +1805,7 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D32" s="12" t="n"/>
